--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6334,0.2855,0.0988,0.0118</t>
-  </si>
-  <si>
-    <t>0.8318,0.0792,0.0618,0.0025</t>
-  </si>
-  <si>
-    <t>0.8795,0.1060,0.0278,0.0009</t>
-  </si>
-  <si>
-    <t>0.8317,0.0853,0.0460,0.0052</t>
-  </si>
-  <si>
-    <t>0.8086,0.0830,0.0579,0.0097</t>
-  </si>
-  <si>
-    <t>0.8310,0.0878,0.0339,0.0043</t>
-  </si>
-  <si>
-    <t>0.8888,0.0413,0.0298,0.0032</t>
-  </si>
-  <si>
-    <t>0.7781,0.0346,0.0314,0.0375</t>
-  </si>
-  <si>
-    <t>0.7503,0.0968,0.0458,0.0138</t>
-  </si>
-  <si>
-    <t>0.8292,0.0695,0.0542,0.0097</t>
-  </si>
-  <si>
-    <t>0.8991,0.0474,0.0245,0.0027</t>
-  </si>
-  <si>
-    <t>0.7827,0.0789,0.0224,0.0143</t>
-  </si>
-  <si>
-    <t>0.9344,0.0335,0.0251,0.0004</t>
-  </si>
-  <si>
-    <t>0.8613,0.0352,0.1167,0.0005</t>
-  </si>
-  <si>
-    <t>0.9074,0.0282,0.0553,0.0004</t>
-  </si>
-  <si>
-    <t>0.9436,0.0226,0.0317,0.0003</t>
-  </si>
-  <si>
-    <t>0.9537,0.0169,0.0185,0.0003</t>
-  </si>
-  <si>
-    <t>0.1446,0.8903,0.0763,0.0010</t>
-  </si>
-  <si>
-    <t>0.7890,0.1715,0.0859,0.0010</t>
-  </si>
-  <si>
-    <t>0.6170,0.4234,0.1047,0.0017</t>
-  </si>
-  <si>
-    <t>0.3296,0.7068,0.1298,0.0049</t>
-  </si>
-  <si>
-    <t>0.1930,0.8273,0.1548,0.0022</t>
-  </si>
-  <si>
-    <t>0.9169,0.0151,0.0715,0.0004</t>
-  </si>
-  <si>
-    <t>0.9292,0.0225,0.0452,0.0004</t>
-  </si>
-  <si>
-    <t>0.9268,0.0041,0.0754,0.0001</t>
-  </si>
-  <si>
-    <t>0.9435,0.0075,0.0441,0.0001</t>
-  </si>
-  <si>
-    <t>0.9663,0.0036,0.0302,0.0001</t>
-  </si>
-  <si>
-    <t>0.8686,0.0242,0.1012,0.0008</t>
-  </si>
-  <si>
-    <t>0.5060,0.0322,0.6402,0.0027</t>
-  </si>
-  <si>
-    <t>0.4443,0.6413,0.0712,0.0014</t>
-  </si>
-  <si>
-    <t>0.8450,0.0986,0.0508,0.0013</t>
-  </si>
-  <si>
-    <t>0.1721,0.1005,0.8635,0.0037</t>
-  </si>
-  <si>
-    <t>0.8305,0.0885,0.0852,0.0003</t>
-  </si>
-  <si>
-    <t>0.7533,0.2040,0.0612,0.0038</t>
-  </si>
-  <si>
-    <t>0.7146,0.1651,0.1376,0.0059</t>
-  </si>
-  <si>
-    <t>0.8499,0.0903,0.0600,0.0016</t>
-  </si>
-  <si>
-    <t>0.9004,0.0813,0.0258,0.0009</t>
-  </si>
-  <si>
-    <t>0.7916,0.1462,0.0196,0.0004</t>
-  </si>
-  <si>
-    <t>0.9532,0.0020,0.0450,0.0001</t>
-  </si>
-  <si>
-    <t>0.9504,0.0015,0.0600,0.0001</t>
-  </si>
-  <si>
-    <t>0.7657,0.0054,0.3664,0.0006</t>
-  </si>
-  <si>
-    <t>0.9008,0.0020,0.2136,0.0001</t>
-  </si>
-  <si>
-    <t>0.5131,0.3912,0.0598,0.0009</t>
-  </si>
-  <si>
-    <t>0.9454,0.0013,0.0885,0.0002</t>
-  </si>
-  <si>
-    <t>0.9173,0.0456,0.0297,0.0006</t>
-  </si>
-  <si>
-    <t>0.4083,0.7488,0.0258,0.0002</t>
-  </si>
-  <si>
-    <t>0.2614,0.7876,0.0843,0.0006</t>
-  </si>
-  <si>
-    <t>0.2859,0.7589,0.1469,0.0011</t>
-  </si>
-  <si>
-    <t>0.8729,0.0056,0.1987,0.0003</t>
-  </si>
-  <si>
-    <t>0.6195,0.0090,0.5592,0.0003</t>
-  </si>
-  <si>
-    <t>0.8822,0.0084,0.1620,0.0002</t>
-  </si>
-  <si>
-    <t>0.8447,0.0184,0.1368,0.0011</t>
-  </si>
-  <si>
-    <t>0.7697,0.0232,0.2751,0.0012</t>
-  </si>
-  <si>
-    <t>0.8182,0.0033,0.2828,0.0002</t>
-  </si>
-  <si>
-    <t>0.7226,0.1362,0.0609,0.0156</t>
-  </si>
-  <si>
-    <t>0.8696,0.0399,0.0458,0.0051</t>
-  </si>
-  <si>
-    <t>0.6942,0.1906,0.1081,0.0095</t>
-  </si>
-  <si>
-    <t>0.1831,0.1375,0.8585,0.0029</t>
-  </si>
-  <si>
-    <t>0.7856,0.0573,0.0677,0.0124</t>
-  </si>
-  <si>
-    <t>0.7299,0.0882,0.1038,0.0214</t>
-  </si>
-  <si>
-    <t>0.7458,0.1524,0.0786,0.0070</t>
-  </si>
-  <si>
-    <t>0.1832,0.5584,0.2977,0.0006</t>
-  </si>
-  <si>
-    <t>0.3421,0.1360,0.5007,0.0003</t>
-  </si>
-  <si>
-    <t>0.8599,0.0068,0.1754,0.0003</t>
-  </si>
-  <si>
-    <t>0.5443,0.0675,0.4179,0.0003</t>
-  </si>
-  <si>
-    <t>0.4951,0.0079,0.7310,0.0002</t>
-  </si>
-  <si>
-    <t>0.7437,0.2892,0.0388,0.0009</t>
-  </si>
-  <si>
-    <t>0.0034,0.9950,0.0387,0.0000</t>
-  </si>
-  <si>
-    <t>0.8146,0.0944,0.0732,0.0039</t>
-  </si>
-  <si>
-    <t>0.8145,0.1160,0.0608,0.0037</t>
-  </si>
-  <si>
-    <t>0.2001,0.4238,0.6395,0.0026</t>
-  </si>
-  <si>
-    <t>0.3264,0.3831,0.2322,0.0001</t>
-  </si>
-  <si>
-    <t>0.6340,0.3381,0.0438,0.0001</t>
-  </si>
-  <si>
-    <t>0.2221,0.7229,0.0530,0.0003</t>
-  </si>
-  <si>
-    <t>0.6927,0.2922,0.0312,0.0001</t>
-  </si>
-  <si>
-    <t>0.9640,0.0055,0.0167,0.0004</t>
-  </si>
-  <si>
-    <t>0.8873,0.0292,0.0511,0.0044</t>
-  </si>
-  <si>
-    <t>0.9432,0.0365,0.0124,0.0007</t>
-  </si>
-  <si>
-    <t>0.9305,0.0226,0.0230,0.0019</t>
-  </si>
-  <si>
-    <t>0.9513,0.0199,0.0116,0.0007</t>
-  </si>
-  <si>
-    <t>0.9593,0.0280,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.6704,0.2496,0.0582,0.0005</t>
-  </si>
-  <si>
-    <t>0.4595,0.1321,0.3099,0.0001</t>
-  </si>
-  <si>
-    <t>0.6962,0.0301,0.3114,0.0001</t>
-  </si>
-  <si>
-    <t>0.6129,0.0267,0.4215,0.0006</t>
-  </si>
-  <si>
-    <t>0.8383,0.0170,0.0888,0.0000</t>
-  </si>
-  <si>
-    <t>0.7778,0.0259,0.2188,0.0002</t>
-  </si>
-  <si>
-    <t>0.8637,0.0493,0.0188,0.0089</t>
-  </si>
-  <si>
-    <t>0.8726,0.0483,0.0432,0.0059</t>
-  </si>
-  <si>
-    <t>0.8824,0.0476,0.0390,0.0032</t>
-  </si>
-  <si>
-    <t>0.6807,0.2457,0.0584,0.0075</t>
-  </si>
-  <si>
-    <t>0.8241,0.0427,0.0220,0.0216</t>
-  </si>
-  <si>
-    <t>0.7477,0.0899,0.0650,0.0165</t>
-  </si>
-  <si>
-    <t>0.4494,0.2902,0.1039,0.0237</t>
-  </si>
-  <si>
-    <t>0.6496,0.1349,0.1146,0.0492</t>
-  </si>
-  <si>
-    <t>0.7526,0.0451,0.0211,0.0372</t>
-  </si>
-  <si>
-    <t>0.6985,0.2553,0.0677,0.0062</t>
-  </si>
-  <si>
-    <t>0.8045,0.0463,0.0458,0.0129</t>
-  </si>
-  <si>
-    <t>0.8253,0.0869,0.0546,0.0061</t>
-  </si>
-  <si>
-    <t>0.8265,0.0564,0.0264,0.0111</t>
-  </si>
-  <si>
-    <t>0.7599,0.0625,0.0490,0.0279</t>
-  </si>
-  <si>
-    <t>0.8573,0.0569,0.0443,0.0068</t>
-  </si>
-  <si>
-    <t>0.8480,0.0351,0.0298,0.0112</t>
-  </si>
-  <si>
-    <t>0.1431,0.0238,0.9226,0.0017</t>
-  </si>
-  <si>
-    <t>0.8782,0.0175,0.1115,0.0005</t>
-  </si>
-  <si>
-    <t>0.9693,0.0077,0.0163,0.0001</t>
-  </si>
-  <si>
-    <t>0.9334,0.0138,0.0456,0.0005</t>
-  </si>
-  <si>
-    <t>0.5443,0.5168,0.0713,0.0034</t>
-  </si>
-  <si>
-    <t>0.6933,0.3166,0.0716,0.0032</t>
-  </si>
-  <si>
-    <t>0.5132,0.4975,0.0778,0.0061</t>
-  </si>
-  <si>
-    <t>0.7329,0.2001,0.0828,0.0033</t>
-  </si>
-  <si>
-    <t>0.2468,0.8163,0.1110,0.0021</t>
-  </si>
-  <si>
-    <t>0.4527,0.5857,0.1056,0.0020</t>
-  </si>
-  <si>
-    <t>0.7219,0.1621,0.1084,0.0061</t>
-  </si>
-  <si>
-    <t>0.7289,0.1783,0.0940,0.0053</t>
-  </si>
-  <si>
-    <t>0.9637,0.0156,0.0109,0.0003</t>
-  </si>
-  <si>
-    <t>0.9154,0.0212,0.0506,0.0007</t>
-  </si>
-  <si>
-    <t>0.9649,0.0083,0.0154,0.0004</t>
-  </si>
-  <si>
-    <t>0.9286,0.0230,0.0296,0.0011</t>
-  </si>
-  <si>
-    <t>0.4274,0.7076,0.0446,0.0010</t>
-  </si>
-  <si>
-    <t>0.5320,0.5564,0.0521,0.0006</t>
-  </si>
-  <si>
-    <t>0.8220,0.1365,0.0507,0.0017</t>
-  </si>
-  <si>
-    <t>0.1489,0.8383,0.1723,0.0015</t>
-  </si>
-  <si>
-    <t>0.7762,0.2745,0.0418,0.0004</t>
-  </si>
-  <si>
-    <t>0.7585,0.1586,0.0913,0.0044</t>
-  </si>
-  <si>
-    <t>0.8422,0.0789,0.0453,0.0048</t>
-  </si>
-  <si>
-    <t>0.7722,0.0722,0.0370,0.0234</t>
-  </si>
-  <si>
-    <t>0.6959,0.1690,0.0876,0.0154</t>
-  </si>
-  <si>
-    <t>0.8051,0.0562,0.0630,0.0140</t>
-  </si>
-  <si>
-    <t>0.8176,0.0755,0.0369,0.0109</t>
-  </si>
-  <si>
-    <t>0.7864,0.1002,0.0611,0.0128</t>
-  </si>
-  <si>
-    <t>0.8912,0.0260,0.0630,0.0017</t>
-  </si>
-  <si>
-    <t>0.7371,0.1968,0.0465,0.0057</t>
-  </si>
-  <si>
-    <t>0.8114,0.1169,0.0592,0.0036</t>
-  </si>
-  <si>
-    <t>0.7925,0.0585,0.0915,0.0002</t>
-  </si>
-  <si>
-    <t>0.7541,0.0514,0.0830,0.0000</t>
-  </si>
-  <si>
-    <t>0.5905,0.0237,0.3160,0.0001</t>
-  </si>
-  <si>
-    <t>0.9451,0.0037,0.0565,0.0001</t>
-  </si>
-  <si>
-    <t>0.9341,0.0230,0.0322,0.0002</t>
-  </si>
-  <si>
-    <t>0.9423,0.0250,0.0195,0.0003</t>
-  </si>
-  <si>
-    <t>0.9023,0.0142,0.1012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9206,0.0245,0.0429,0.0008</t>
-  </si>
-  <si>
-    <t>0.8463,0.0959,0.0473,0.0034</t>
-  </si>
-  <si>
-    <t>0.9440,0.0117,0.0049,0.0039</t>
-  </si>
-  <si>
-    <t>0.9240,0.0389,0.0208,0.0013</t>
-  </si>
-  <si>
-    <t>0.9499,0.0068,0.0121,0.0030</t>
-  </si>
-  <si>
-    <t>0.3790,0.4252,0.1802,0.0013</t>
-  </si>
-  <si>
-    <t>0.8005,0.0773,0.0414,0.0126</t>
-  </si>
-  <si>
-    <t>0.7568,0.2059,0.0665,0.0030</t>
-  </si>
-  <si>
-    <t>0.7434,0.1255,0.0881,0.0166</t>
-  </si>
-  <si>
-    <t>0.7474,0.1606,0.1026,0.0084</t>
-  </si>
-  <si>
-    <t>0.8975,0.0407,0.0374,0.0013</t>
-  </si>
-  <si>
-    <t>0.7663,0.1616,0.0457,0.0039</t>
-  </si>
-  <si>
-    <t>0.7560,0.1179,0.0603,0.0111</t>
-  </si>
-  <si>
-    <t>0.1428,0.2586,0.8248,0.0070</t>
-  </si>
-  <si>
-    <t>0.7574,0.1158,0.0728,0.0117</t>
-  </si>
-  <si>
-    <t>0.7138,0.1667,0.0981,0.0129</t>
-  </si>
-  <si>
-    <t>0.8753,0.0891,0.0280,0.0015</t>
-  </si>
-  <si>
-    <t>0.8877,0.0302,0.0408,0.0040</t>
-  </si>
-  <si>
-    <t>0.7707,0.1784,0.0679,0.0016</t>
-  </si>
-  <si>
-    <t>0.7155,0.3072,0.0488,0.0008</t>
-  </si>
-  <si>
-    <t>0.9359,0.0363,0.0222,0.0004</t>
-  </si>
-  <si>
-    <t>0.7649,0.1989,0.0724,0.0020</t>
-  </si>
-  <si>
-    <t>0.8752,0.0493,0.0440,0.0072</t>
-  </si>
-  <si>
-    <t>0.8352,0.0526,0.0348,0.0121</t>
-  </si>
-  <si>
-    <t>0.7589,0.0798,0.0618,0.0217</t>
-  </si>
-  <si>
-    <t>0.7766,0.1125,0.0362,0.0121</t>
-  </si>
-  <si>
-    <t>0.8082,0.0428,0.0371,0.0185</t>
-  </si>
-  <si>
-    <t>0.8061,0.0800,0.0434,0.0125</t>
-  </si>
-  <si>
-    <t>0.6481,0.2201,0.0684,0.0163</t>
-  </si>
-  <si>
-    <t>0.6659,0.2069,0.0642,0.0103</t>
-  </si>
-  <si>
-    <t>0.3870,0.6257,0.1419,0.0050</t>
-  </si>
-  <si>
-    <t>0.8590,0.0744,0.0357,0.0027</t>
-  </si>
-  <si>
-    <t>0.8205,0.1596,0.0438,0.0018</t>
-  </si>
-  <si>
-    <t>0.7646,0.1596,0.0742,0.0035</t>
-  </si>
-  <si>
-    <t>0.8586,0.0709,0.0289,0.0061</t>
-  </si>
-  <si>
-    <t>0.6406,0.2505,0.1102,0.0118</t>
-  </si>
-  <si>
-    <t>0.7829,0.1720,0.0471,0.0027</t>
-  </si>
-  <si>
-    <t>0.6775,0.1588,0.1177,0.0163</t>
-  </si>
-  <si>
-    <t>0.6321,0.0340,0.5041,0.0023</t>
-  </si>
-  <si>
-    <t>0.7265,0.0920,0.0675,0.0235</t>
-  </si>
-  <si>
-    <t>0.8144,0.0052,0.3049,0.0001</t>
-  </si>
-  <si>
-    <t>0.9061,0.0045,0.1346,0.0001</t>
-  </si>
-  <si>
-    <t>0.7572,0.0249,0.2857,0.0002</t>
-  </si>
-  <si>
-    <t>0.3552,0.0419,0.7277,0.0015</t>
-  </si>
-  <si>
-    <t>0.8678,0.0043,0.2015,0.0003</t>
-  </si>
-  <si>
-    <t>0.5596,0.0193,0.5467,0.0004</t>
-  </si>
-  <si>
-    <t>0.8612,0.0078,0.1740,0.0001</t>
-  </si>
-  <si>
-    <t>0.9273,0.0253,0.0426,0.0004</t>
-  </si>
-  <si>
-    <t>0.9296,0.0210,0.0439,0.0003</t>
-  </si>
-  <si>
-    <t>0.8590,0.0661,0.0659,0.0008</t>
-  </si>
-  <si>
-    <t>0.9057,0.0359,0.0526,0.0004</t>
-  </si>
-  <si>
-    <t>0.7676,0.1895,0.0938,0.0013</t>
-  </si>
-  <si>
-    <t>0.8932,0.0226,0.0951,0.0005</t>
-  </si>
-  <si>
-    <t>0.9387,0.0371,0.0153,0.0006</t>
-  </si>
-  <si>
-    <t>0.8304,0.0939,0.0613,0.0004</t>
-  </si>
-  <si>
-    <t>0.6180,0.3159,0.1050,0.0082</t>
-  </si>
-  <si>
-    <t>0.8008,0.1223,0.0335,0.0084</t>
-  </si>
-  <si>
-    <t>0.5739,0.3252,0.1226,0.0121</t>
-  </si>
-  <si>
-    <t>0.6378,0.2946,0.0674,0.0098</t>
-  </si>
-  <si>
-    <t>0.6065,0.2654,0.0749,0.0141</t>
-  </si>
-  <si>
-    <t>0.9367,0.0214,0.0214,0.0007</t>
-  </si>
-  <si>
-    <t>0.9033,0.0287,0.0651,0.0005</t>
-  </si>
-  <si>
-    <t>0.9389,0.0123,0.0477,0.0003</t>
-  </si>
-  <si>
-    <t>0.9622,0.0050,0.0295,0.0002</t>
-  </si>
-  <si>
-    <t>0.9282,0.0095,0.0530,0.0005</t>
-  </si>
-  <si>
-    <t>0.4570,0.0399,0.6900,0.0006</t>
-  </si>
-  <si>
-    <t>0.9700,0.0102,0.0096,0.0002</t>
-  </si>
-  <si>
-    <t>0.9845,0.0012,0.0107,0.0000</t>
-  </si>
-  <si>
-    <t>0.9463,0.0037,0.0412,0.0002</t>
-  </si>
-  <si>
-    <t>0.9625,0.0075,0.0171,0.0001</t>
-  </si>
-  <si>
-    <t>0.7695,0.0782,0.0531,0.0203</t>
-  </si>
-  <si>
-    <t>0.7332,0.1227,0.1141,0.0103</t>
-  </si>
-  <si>
-    <t>0.6515,0.2213,0.0597,0.0123</t>
-  </si>
-  <si>
-    <t>0.8344,0.0556,0.0901,0.0032</t>
-  </si>
-  <si>
-    <t>0.8883,0.0290,0.0236,0.0079</t>
-  </si>
-  <si>
-    <t>0.7155,0.0964,0.0844,0.0176</t>
-  </si>
-  <si>
-    <t>0.8684,0.0549,0.0454,0.0051</t>
-  </si>
-  <si>
-    <t>0.7229,0.0739,0.0315,0.0245</t>
-  </si>
-  <si>
-    <t>0.8884,0.0435,0.0537,0.0006</t>
-  </si>
-  <si>
-    <t>0.8582,0.0652,0.0455,0.0045</t>
-  </si>
-  <si>
-    <t>0.7869,0.1581,0.0464,0.0035</t>
-  </si>
-  <si>
-    <t>0.8234,0.0018,0.3198,0.0001</t>
-  </si>
-  <si>
-    <t>0.7749,0.0099,0.2396,0.0008</t>
-  </si>
-  <si>
-    <t>0.9199,0.0199,0.0559,0.0003</t>
-  </si>
-  <si>
-    <t>0.2594,0.0113,0.8661,0.0002</t>
-  </si>
-  <si>
-    <t>0.9470,0.0065,0.0451,0.0002</t>
-  </si>
-  <si>
-    <t>0.6083,0.0108,0.4650,0.0006</t>
-  </si>
-  <si>
-    <t>0.9306,0.0010,0.1405,0.0000</t>
-  </si>
-  <si>
-    <t>0.8004,0.1049,0.0612,0.0003</t>
-  </si>
-  <si>
-    <t>0.9496,0.0134,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.9421,0.0115,0.0427,0.0003</t>
-  </si>
-  <si>
-    <t>0.9373,0.0340,0.0223,0.0002</t>
-  </si>
-  <si>
-    <t>0.8427,0.0641,0.0281,0.0072</t>
-  </si>
-  <si>
-    <t>0.8733,0.0253,0.0233,0.0124</t>
-  </si>
-  <si>
-    <t>0.8133,0.0940,0.0272,0.0097</t>
-  </si>
-  <si>
-    <t>0.8439,0.0891,0.0638,0.0033</t>
-  </si>
-  <si>
-    <t>0.8176,0.0328,0.0326,0.0218</t>
-  </si>
-  <si>
-    <t>0.7763,0.1082,0.0571,0.0114</t>
-  </si>
-  <si>
-    <t>0.7027,0.1100,0.1036,0.0242</t>
-  </si>
-  <si>
-    <t>0.5817,0.1944,0.0458,0.0224</t>
-  </si>
-  <si>
-    <t>0.8911,0.0115,0.1002,0.0002</t>
-  </si>
-  <si>
-    <t>0.6599,0.0353,0.2951,0.0002</t>
-  </si>
-  <si>
-    <t>0.7631,0.0032,0.4352,0.0001</t>
-  </si>
-  <si>
-    <t>0.9592,0.0047,0.0291,0.0001</t>
-  </si>
-  <si>
-    <t>0.8991,0.0016,0.1976,0.0001</t>
-  </si>
-  <si>
-    <t>0.9714,0.0026,0.0159,0.0002</t>
-  </si>
-  <si>
-    <t>0.8350,0.0349,0.1389,0.0005</t>
-  </si>
-  <si>
-    <t>0.9633,0.0028,0.0235,0.0003</t>
-  </si>
-  <si>
-    <t>0.8305,0.0649,0.0353,0.0091</t>
-  </si>
-  <si>
-    <t>0.9257,0.0490,0.0250,0.0013</t>
-  </si>
-  <si>
-    <t>0.9642,0.0074,0.0120,0.0012</t>
-  </si>
-  <si>
-    <t>0.8168,0.0528,0.0471,0.0146</t>
-  </si>
-  <si>
-    <t>0.8499,0.0211,0.0256,0.0189</t>
-  </si>
-  <si>
-    <t>0.9482,0.0131,0.0208,0.0006</t>
+    <t>0.8596,0.0490,0.0848,0.0008</t>
+  </si>
+  <si>
+    <t>0.8427,0.0614,0.0246,0.0088</t>
+  </si>
+  <si>
+    <t>0.7601,0.0860,0.1114,0.0138</t>
+  </si>
+  <si>
+    <t>0.8031,0.1660,0.0430,0.0028</t>
+  </si>
+  <si>
+    <t>0.7809,0.1700,0.0428,0.0039</t>
+  </si>
+  <si>
+    <t>0.8383,0.0480,0.0693,0.0054</t>
+  </si>
+  <si>
+    <t>0.6371,0.2070,0.0668,0.0216</t>
+  </si>
+  <si>
+    <t>0.6743,0.0936,0.0882,0.0396</t>
+  </si>
+  <si>
+    <t>0.8234,0.0812,0.0749,0.0065</t>
+  </si>
+  <si>
+    <t>0.8581,0.0506,0.0453,0.0075</t>
+  </si>
+  <si>
+    <t>0.8015,0.0923,0.0596,0.0098</t>
+  </si>
+  <si>
+    <t>0.7198,0.1306,0.1113,0.0119</t>
+  </si>
+  <si>
+    <t>0.9493,0.0196,0.0247,0.0002</t>
+  </si>
+  <si>
+    <t>0.8658,0.0526,0.0799,0.0010</t>
+  </si>
+  <si>
+    <t>0.8524,0.0181,0.1659,0.0004</t>
+  </si>
+  <si>
+    <t>0.8418,0.0313,0.1542,0.0004</t>
+  </si>
+  <si>
+    <t>0.8829,0.0518,0.0541,0.0015</t>
+  </si>
+  <si>
+    <t>0.2346,0.8467,0.0542,0.0007</t>
+  </si>
+  <si>
+    <t>0.5871,0.4550,0.0704,0.0013</t>
+  </si>
+  <si>
+    <t>0.8202,0.1240,0.0621,0.0011</t>
+  </si>
+  <si>
+    <t>0.3765,0.6494,0.1024,0.0020</t>
+  </si>
+  <si>
+    <t>0.1867,0.8432,0.0863,0.0006</t>
+  </si>
+  <si>
+    <t>0.9029,0.0176,0.0823,0.0006</t>
+  </si>
+  <si>
+    <t>0.9835,0.0034,0.0085,0.0000</t>
+  </si>
+  <si>
+    <t>0.9115,0.0101,0.0860,0.0002</t>
+  </si>
+  <si>
+    <t>0.9506,0.0051,0.0414,0.0002</t>
+  </si>
+  <si>
+    <t>0.9257,0.0080,0.0951,0.0002</t>
+  </si>
+  <si>
+    <t>0.7905,0.0508,0.1258,0.0004</t>
+  </si>
+  <si>
+    <t>0.6719,0.0075,0.4861,0.0014</t>
+  </si>
+  <si>
+    <t>0.5649,0.3369,0.1946,0.0039</t>
+  </si>
+  <si>
+    <t>0.7494,0.1506,0.1016,0.0032</t>
+  </si>
+  <si>
+    <t>0.0968,0.0442,0.9482,0.0024</t>
+  </si>
+  <si>
+    <t>0.6840,0.2185,0.1312,0.0021</t>
+  </si>
+  <si>
+    <t>0.8562,0.0714,0.0573,0.0016</t>
+  </si>
+  <si>
+    <t>0.7853,0.1107,0.0792,0.0067</t>
+  </si>
+  <si>
+    <t>0.8095,0.1132,0.0632,0.0046</t>
+  </si>
+  <si>
+    <t>0.8422,0.1309,0.0513,0.0008</t>
+  </si>
+  <si>
+    <t>0.5054,0.4845,0.0154,0.0007</t>
+  </si>
+  <si>
+    <t>0.9043,0.0011,0.1234,0.0002</t>
+  </si>
+  <si>
+    <t>0.9626,0.0021,0.0408,0.0001</t>
+  </si>
+  <si>
+    <t>0.9271,0.0036,0.0724,0.0002</t>
+  </si>
+  <si>
+    <t>0.9644,0.0039,0.0327,0.0001</t>
+  </si>
+  <si>
+    <t>0.3519,0.4715,0.1341,0.0008</t>
+  </si>
+  <si>
+    <t>0.9115,0.0024,0.0932,0.0006</t>
+  </si>
+  <si>
+    <t>0.9318,0.0317,0.0219,0.0010</t>
+  </si>
+  <si>
+    <t>0.7499,0.3003,0.0445,0.0008</t>
+  </si>
+  <si>
+    <t>0.2495,0.8052,0.0471,0.0001</t>
+  </si>
+  <si>
+    <t>0.7217,0.3167,0.0599,0.0005</t>
+  </si>
+  <si>
+    <t>0.1828,0.0545,0.8357,0.0005</t>
+  </si>
+  <si>
+    <t>0.7715,0.0063,0.3909,0.0004</t>
+  </si>
+  <si>
+    <t>0.9019,0.0084,0.1092,0.0002</t>
+  </si>
+  <si>
+    <t>0.8054,0.0051,0.3302,0.0001</t>
+  </si>
+  <si>
+    <t>0.7774,0.0102,0.3252,0.0002</t>
+  </si>
+  <si>
+    <t>0.9171,0.0032,0.1223,0.0001</t>
+  </si>
+  <si>
+    <t>0.6711,0.2470,0.0708,0.0125</t>
+  </si>
+  <si>
+    <t>0.8515,0.0554,0.0390,0.0049</t>
+  </si>
+  <si>
+    <t>0.7445,0.1001,0.0674,0.0157</t>
+  </si>
+  <si>
+    <t>0.2426,0.0984,0.8400,0.0034</t>
+  </si>
+  <si>
+    <t>0.8098,0.0615,0.0329,0.0153</t>
+  </si>
+  <si>
+    <t>0.8680,0.0306,0.0462,0.0067</t>
+  </si>
+  <si>
+    <t>0.7473,0.1203,0.1148,0.0100</t>
+  </si>
+  <si>
+    <t>0.2895,0.2794,0.4308,0.0014</t>
+  </si>
+  <si>
+    <t>0.8277,0.0053,0.2828,0.0001</t>
+  </si>
+  <si>
+    <t>0.9033,0.0027,0.1277,0.0001</t>
+  </si>
+  <si>
+    <t>0.2801,0.4159,0.2686,0.0002</t>
+  </si>
+  <si>
+    <t>0.6636,0.0046,0.5616,0.0002</t>
+  </si>
+  <si>
+    <t>0.9372,0.0482,0.0153,0.0003</t>
+  </si>
+  <si>
+    <t>0.0157,0.9884,0.0161,0.0001</t>
+  </si>
+  <si>
+    <t>0.9510,0.0284,0.0133,0.0006</t>
+  </si>
+  <si>
+    <t>0.8518,0.1213,0.0491,0.0008</t>
+  </si>
+  <si>
+    <t>0.1522,0.2007,0.8476,0.0008</t>
+  </si>
+  <si>
+    <t>0.9364,0.0166,0.0377,0.0001</t>
+  </si>
+  <si>
+    <t>0.9426,0.0223,0.0256,0.0001</t>
+  </si>
+  <si>
+    <t>0.1352,0.8580,0.0272,0.0001</t>
+  </si>
+  <si>
+    <t>0.2650,0.3161,0.2479,0.0002</t>
+  </si>
+  <si>
+    <t>0.9664,0.0077,0.0100,0.0003</t>
+  </si>
+  <si>
+    <t>0.8556,0.0464,0.0499,0.0055</t>
+  </si>
+  <si>
+    <t>0.9276,0.0336,0.0142,0.0025</t>
+  </si>
+  <si>
+    <t>0.9572,0.0247,0.0111,0.0005</t>
+  </si>
+  <si>
+    <t>0.8484,0.0491,0.0692,0.0045</t>
+  </si>
+  <si>
+    <t>0.9571,0.0092,0.0163,0.0008</t>
+  </si>
+  <si>
+    <t>0.7364,0.0623,0.1183,0.0001</t>
+  </si>
+  <si>
+    <t>0.7659,0.0152,0.2477,0.0001</t>
+  </si>
+  <si>
+    <t>0.9038,0.0181,0.0552,0.0001</t>
+  </si>
+  <si>
+    <t>0.7212,0.0427,0.2078,0.0006</t>
+  </si>
+  <si>
+    <t>0.5970,0.2847,0.1057,0.0002</t>
+  </si>
+  <si>
+    <t>0.8983,0.0128,0.0987,0.0003</t>
+  </si>
+  <si>
+    <t>0.6389,0.2809,0.1124,0.0115</t>
+  </si>
+  <si>
+    <t>0.7913,0.0556,0.0510,0.0157</t>
+  </si>
+  <si>
+    <t>0.8424,0.0674,0.0393,0.0071</t>
+  </si>
+  <si>
+    <t>0.7831,0.0784,0.0372,0.0162</t>
+  </si>
+  <si>
+    <t>0.8317,0.0636,0.0614,0.0040</t>
+  </si>
+  <si>
+    <t>0.8116,0.0376,0.0574,0.0227</t>
+  </si>
+  <si>
+    <t>0.8365,0.0279,0.0239,0.0254</t>
+  </si>
+  <si>
+    <t>0.7973,0.0528,0.0640,0.0155</t>
+  </si>
+  <si>
+    <t>0.6801,0.1450,0.0477,0.0203</t>
+  </si>
+  <si>
+    <t>0.9253,0.0162,0.0091,0.0068</t>
+  </si>
+  <si>
+    <t>0.7434,0.0997,0.0353,0.0247</t>
+  </si>
+  <si>
+    <t>0.8419,0.0387,0.0211,0.0211</t>
+  </si>
+  <si>
+    <t>0.7368,0.1282,0.0468,0.0143</t>
+  </si>
+  <si>
+    <t>0.7730,0.0735,0.0494,0.0242</t>
+  </si>
+  <si>
+    <t>0.6411,0.3001,0.1067,0.0072</t>
+  </si>
+  <si>
+    <t>0.8948,0.0214,0.0120,0.0115</t>
+  </si>
+  <si>
+    <t>0.2638,0.0174,0.8473,0.0006</t>
+  </si>
+  <si>
+    <t>0.6913,0.0255,0.4239,0.0016</t>
+  </si>
+  <si>
+    <t>0.9638,0.0058,0.0223,0.0005</t>
+  </si>
+  <si>
+    <t>0.9171,0.0050,0.1214,0.0002</t>
+  </si>
+  <si>
+    <t>0.7225,0.2739,0.0596,0.0011</t>
+  </si>
+  <si>
+    <t>0.6007,0.3387,0.1178,0.0024</t>
+  </si>
+  <si>
+    <t>0.4583,0.5669,0.0920,0.0039</t>
+  </si>
+  <si>
+    <t>0.7795,0.1744,0.0437,0.0041</t>
+  </si>
+  <si>
+    <t>0.2415,0.7906,0.1605,0.0028</t>
+  </si>
+  <si>
+    <t>0.4069,0.6402,0.1084,0.0005</t>
+  </si>
+  <si>
+    <t>0.7248,0.1978,0.1037,0.0036</t>
+  </si>
+  <si>
+    <t>0.9628,0.0072,0.0191,0.0003</t>
+  </si>
+  <si>
+    <t>0.9431,0.0049,0.0688,0.0001</t>
+  </si>
+  <si>
+    <t>0.9596,0.0121,0.0174,0.0002</t>
+  </si>
+  <si>
+    <t>0.9615,0.0136,0.0146,0.0002</t>
+  </si>
+  <si>
+    <t>0.8617,0.0756,0.0651,0.0010</t>
+  </si>
+  <si>
+    <t>0.4912,0.5709,0.0703,0.0005</t>
+  </si>
+  <si>
+    <t>0.2224,0.8636,0.0300,0.0021</t>
+  </si>
+  <si>
+    <t>0.8339,0.1448,0.0365,0.0009</t>
+  </si>
+  <si>
+    <t>0.2895,0.6849,0.1763,0.0014</t>
+  </si>
+  <si>
+    <t>0.8124,0.1489,0.0578,0.0012</t>
+  </si>
+  <si>
+    <t>0.8419,0.0669,0.0681,0.0031</t>
+  </si>
+  <si>
+    <t>0.7542,0.1593,0.0888,0.0033</t>
+  </si>
+  <si>
+    <t>0.8164,0.0559,0.0328,0.0174</t>
+  </si>
+  <si>
+    <t>0.6881,0.2034,0.0993,0.0077</t>
+  </si>
+  <si>
+    <t>0.7015,0.1415,0.0814,0.0161</t>
+  </si>
+  <si>
+    <t>0.8737,0.0315,0.0411,0.0072</t>
+  </si>
+  <si>
+    <t>0.8831,0.0419,0.0358,0.0061</t>
+  </si>
+  <si>
+    <t>0.8760,0.0468,0.0420,0.0037</t>
+  </si>
+  <si>
+    <t>0.8418,0.0460,0.0488,0.0096</t>
+  </si>
+  <si>
+    <t>0.7756,0.0826,0.0641,0.0118</t>
+  </si>
+  <si>
+    <t>0.8453,0.0098,0.2488,0.0002</t>
+  </si>
+  <si>
+    <t>0.7727,0.1267,0.0619,0.0003</t>
+  </si>
+  <si>
+    <t>0.8898,0.0040,0.1381,0.0001</t>
+  </si>
+  <si>
+    <t>0.8928,0.0068,0.1179,0.0001</t>
+  </si>
+  <si>
+    <t>0.9644,0.0129,0.0118,0.0003</t>
+  </si>
+  <si>
+    <t>0.9463,0.0123,0.0405,0.0002</t>
+  </si>
+  <si>
+    <t>0.9193,0.0125,0.0805,0.0002</t>
+  </si>
+  <si>
+    <t>0.9365,0.0353,0.0185,0.0002</t>
+  </si>
+  <si>
+    <t>0.9514,0.0071,0.0233,0.0010</t>
+  </si>
+  <si>
+    <t>0.8968,0.0192,0.0302,0.0071</t>
+  </si>
+  <si>
+    <t>0.9398,0.0225,0.0185,0.0014</t>
+  </si>
+  <si>
+    <t>0.9042,0.0278,0.0337,0.0045</t>
+  </si>
+  <si>
+    <t>0.6008,0.3467,0.0629,0.0010</t>
+  </si>
+  <si>
+    <t>0.8020,0.0901,0.0772,0.0072</t>
+  </si>
+  <si>
+    <t>0.8119,0.1200,0.0578,0.0017</t>
+  </si>
+  <si>
+    <t>0.8091,0.0719,0.0501,0.0107</t>
+  </si>
+  <si>
+    <t>0.8083,0.1350,0.0643,0.0042</t>
+  </si>
+  <si>
+    <t>0.8597,0.0392,0.0678,0.0024</t>
+  </si>
+  <si>
+    <t>0.9316,0.0311,0.0185,0.0011</t>
+  </si>
+  <si>
+    <t>0.7841,0.0810,0.0542,0.0145</t>
+  </si>
+  <si>
+    <t>0.3810,0.1565,0.5629,0.0129</t>
+  </si>
+  <si>
+    <t>0.8049,0.1048,0.0462,0.0099</t>
+  </si>
+  <si>
+    <t>0.7263,0.1695,0.0617,0.0116</t>
+  </si>
+  <si>
+    <t>0.8102,0.1023,0.0964,0.0010</t>
+  </si>
+  <si>
+    <t>0.8978,0.0254,0.0520,0.0023</t>
+  </si>
+  <si>
+    <t>0.9241,0.0427,0.0271,0.0007</t>
+  </si>
+  <si>
+    <t>0.8472,0.0802,0.0449,0.0043</t>
+  </si>
+  <si>
+    <t>0.8538,0.1288,0.0336,0.0010</t>
+  </si>
+  <si>
+    <t>0.9267,0.0349,0.0244,0.0009</t>
+  </si>
+  <si>
+    <t>0.7589,0.1090,0.0802,0.0109</t>
+  </si>
+  <si>
+    <t>0.7548,0.1185,0.0639,0.0095</t>
+  </si>
+  <si>
+    <t>0.7997,0.0805,0.0621,0.0157</t>
+  </si>
+  <si>
+    <t>0.7593,0.1345,0.0751,0.0064</t>
+  </si>
+  <si>
+    <t>0.7616,0.0887,0.0564,0.0150</t>
+  </si>
+  <si>
+    <t>0.8204,0.0909,0.0341,0.0047</t>
+  </si>
+  <si>
+    <t>0.7396,0.0872,0.0722,0.0172</t>
+  </si>
+  <si>
+    <t>0.8856,0.0601,0.0272,0.0021</t>
+  </si>
+  <si>
+    <t>0.5048,0.4735,0.0947,0.0082</t>
+  </si>
+  <si>
+    <t>0.8616,0.1074,0.0401,0.0013</t>
+  </si>
+  <si>
+    <t>0.8061,0.1037,0.0859,0.0054</t>
+  </si>
+  <si>
+    <t>0.5185,0.3678,0.1739,0.0108</t>
+  </si>
+  <si>
+    <t>0.7334,0.2052,0.1116,0.0025</t>
+  </si>
+  <si>
+    <t>0.8889,0.0351,0.0394,0.0044</t>
+  </si>
+  <si>
+    <t>0.6846,0.1904,0.1025,0.0129</t>
+  </si>
+  <si>
+    <t>0.7055,0.1758,0.1372,0.0024</t>
+  </si>
+  <si>
+    <t>0.0981,0.0542,0.9443,0.0005</t>
+  </si>
+  <si>
+    <t>0.7782,0.1678,0.0333,0.0032</t>
+  </si>
+  <si>
+    <t>0.9118,0.0058,0.0703,0.0000</t>
+  </si>
+  <si>
+    <t>0.9518,0.0015,0.0565,0.0001</t>
+  </si>
+  <si>
+    <t>0.7950,0.0344,0.1897,0.0005</t>
+  </si>
+  <si>
+    <t>0.7637,0.0624,0.1348,0.0007</t>
+  </si>
+  <si>
+    <t>0.9524,0.0011,0.0757,0.0000</t>
+  </si>
+  <si>
+    <t>0.9183,0.0008,0.1549,0.0000</t>
+  </si>
+  <si>
+    <t>0.9129,0.0032,0.1345,0.0001</t>
+  </si>
+  <si>
+    <t>0.9384,0.0130,0.0467,0.0001</t>
+  </si>
+  <si>
+    <t>0.9449,0.0211,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.9279,0.0390,0.0241,0.0003</t>
+  </si>
+  <si>
+    <t>0.7635,0.1356,0.1211,0.0008</t>
+  </si>
+  <si>
+    <t>0.8706,0.0561,0.0673,0.0003</t>
+  </si>
+  <si>
+    <t>0.9328,0.0271,0.0315,0.0003</t>
+  </si>
+  <si>
+    <t>0.9389,0.0174,0.0281,0.0009</t>
+  </si>
+  <si>
+    <t>0.8674,0.1014,0.0397,0.0014</t>
+  </si>
+  <si>
+    <t>0.6142,0.3223,0.0912,0.0056</t>
+  </si>
+  <si>
+    <t>0.6585,0.2527,0.0765,0.0069</t>
+  </si>
+  <si>
+    <t>0.7217,0.1382,0.0684,0.0125</t>
+  </si>
+  <si>
+    <t>0.7198,0.1518,0.0391,0.0115</t>
+  </si>
+  <si>
+    <t>0.7793,0.0910,0.0434,0.0133</t>
+  </si>
+  <si>
+    <t>0.9130,0.0505,0.0263,0.0005</t>
+  </si>
+  <si>
+    <t>0.8070,0.0351,0.1779,0.0029</t>
+  </si>
+  <si>
+    <t>0.9128,0.0225,0.0512,0.0005</t>
+  </si>
+  <si>
+    <t>0.9474,0.0206,0.0217,0.0004</t>
+  </si>
+  <si>
+    <t>0.9071,0.0293,0.0499,0.0010</t>
+  </si>
+  <si>
+    <t>0.8338,0.0227,0.1451,0.0004</t>
+  </si>
+  <si>
+    <t>0.8253,0.0687,0.0585,0.0003</t>
+  </si>
+  <si>
+    <t>0.8956,0.0057,0.1171,0.0005</t>
+  </si>
+  <si>
+    <t>0.9495,0.0011,0.0663,0.0001</t>
+  </si>
+  <si>
+    <t>0.8810,0.0227,0.0747,0.0003</t>
+  </si>
+  <si>
+    <t>0.6436,0.2216,0.0539,0.0148</t>
+  </si>
+  <si>
+    <t>0.7670,0.1412,0.0454,0.0062</t>
+  </si>
+  <si>
+    <t>0.7573,0.0993,0.0493,0.0170</t>
+  </si>
+  <si>
+    <t>0.8310,0.0678,0.0498,0.0089</t>
+  </si>
+  <si>
+    <t>0.7108,0.1584,0.0988,0.0123</t>
+  </si>
+  <si>
+    <t>0.5784,0.2902,0.0608,0.0147</t>
+  </si>
+  <si>
+    <t>0.6462,0.2234,0.0823,0.0090</t>
+  </si>
+  <si>
+    <t>0.5763,0.2055,0.0430,0.0261</t>
+  </si>
+  <si>
+    <t>0.8403,0.0259,0.1683,0.0008</t>
+  </si>
+  <si>
+    <t>0.8642,0.0720,0.0586,0.0009</t>
+  </si>
+  <si>
+    <t>0.6432,0.2639,0.1072,0.0071</t>
+  </si>
+  <si>
+    <t>0.1830,0.0363,0.8994,0.0003</t>
+  </si>
+  <si>
+    <t>0.5931,0.0086,0.5413,0.0007</t>
+  </si>
+  <si>
+    <t>0.8216,0.0389,0.1693,0.0006</t>
+  </si>
+  <si>
+    <t>0.3495,0.0071,0.8186,0.0001</t>
+  </si>
+  <si>
+    <t>0.7470,0.0458,0.2193,0.0001</t>
+  </si>
+  <si>
+    <t>0.1849,0.0264,0.8947,0.0005</t>
+  </si>
+  <si>
+    <t>0.9444,0.0056,0.0404,0.0002</t>
+  </si>
+  <si>
+    <t>0.8270,0.0380,0.1719,0.0007</t>
+  </si>
+  <si>
+    <t>0.8003,0.1297,0.0649,0.0029</t>
+  </si>
+  <si>
+    <t>0.9645,0.0051,0.0203,0.0002</t>
+  </si>
+  <si>
+    <t>0.9687,0.0115,0.0118,0.0001</t>
+  </si>
+  <si>
+    <t>0.6489,0.1437,0.0829,0.0272</t>
+  </si>
+  <si>
+    <t>0.8615,0.0742,0.0403,0.0037</t>
+  </si>
+  <si>
+    <t>0.8386,0.0392,0.0252,0.0093</t>
+  </si>
+  <si>
+    <t>0.8597,0.0764,0.0485,0.0028</t>
+  </si>
+  <si>
+    <t>0.5921,0.1084,0.0369,0.0453</t>
+  </si>
+  <si>
+    <t>0.7219,0.1026,0.0534,0.0172</t>
+  </si>
+  <si>
+    <t>0.7356,0.1076,0.1109,0.0147</t>
+  </si>
+  <si>
+    <t>0.7665,0.1231,0.0692,0.0090</t>
+  </si>
+  <si>
+    <t>0.7711,0.0304,0.2294,0.0004</t>
+  </si>
+  <si>
+    <t>0.0476,0.8949,0.2827,0.0002</t>
+  </si>
+  <si>
+    <t>0.9146,0.0115,0.0645,0.0002</t>
+  </si>
+  <si>
+    <t>0.9482,0.0076,0.0339,0.0002</t>
+  </si>
+  <si>
+    <t>0.9112,0.0028,0.1343,0.0001</t>
+  </si>
+  <si>
+    <t>0.8956,0.0119,0.0958,0.0004</t>
+  </si>
+  <si>
+    <t>0.9080,0.0088,0.0921,0.0005</t>
+  </si>
+  <si>
+    <t>0.9321,0.0088,0.0532,0.0003</t>
+  </si>
+  <si>
+    <t>0.8969,0.0555,0.0297,0.0021</t>
+  </si>
+  <si>
+    <t>0.9513,0.0248,0.0101,0.0009</t>
+  </si>
+  <si>
+    <t>0.9104,0.0464,0.0234,0.0034</t>
+  </si>
+  <si>
+    <t>0.9570,0.0063,0.0197,0.0006</t>
+  </si>
+  <si>
+    <t>0.8912,0.0147,0.0107,0.0155</t>
+  </si>
+  <si>
+    <t>0.8757,0.0540,0.0469,0.0026</t>
   </si>
 </sst>
 </file>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8596,0.0490,0.0848,0.0008</t>
-  </si>
-  <si>
-    <t>0.8427,0.0614,0.0246,0.0088</t>
-  </si>
-  <si>
-    <t>0.7601,0.0860,0.1114,0.0138</t>
-  </si>
-  <si>
-    <t>0.8031,0.1660,0.0430,0.0028</t>
-  </si>
-  <si>
-    <t>0.7809,0.1700,0.0428,0.0039</t>
-  </si>
-  <si>
-    <t>0.8383,0.0480,0.0693,0.0054</t>
-  </si>
-  <si>
-    <t>0.6371,0.2070,0.0668,0.0216</t>
-  </si>
-  <si>
-    <t>0.6743,0.0936,0.0882,0.0396</t>
-  </si>
-  <si>
-    <t>0.8234,0.0812,0.0749,0.0065</t>
-  </si>
-  <si>
-    <t>0.8581,0.0506,0.0453,0.0075</t>
-  </si>
-  <si>
-    <t>0.8015,0.0923,0.0596,0.0098</t>
-  </si>
-  <si>
-    <t>0.7198,0.1306,0.1113,0.0119</t>
-  </si>
-  <si>
-    <t>0.9493,0.0196,0.0247,0.0002</t>
-  </si>
-  <si>
-    <t>0.8658,0.0526,0.0799,0.0010</t>
-  </si>
-  <si>
-    <t>0.8524,0.0181,0.1659,0.0004</t>
-  </si>
-  <si>
-    <t>0.8418,0.0313,0.1542,0.0004</t>
-  </si>
-  <si>
-    <t>0.8829,0.0518,0.0541,0.0015</t>
-  </si>
-  <si>
-    <t>0.2346,0.8467,0.0542,0.0007</t>
-  </si>
-  <si>
-    <t>0.5871,0.4550,0.0704,0.0013</t>
-  </si>
-  <si>
-    <t>0.8202,0.1240,0.0621,0.0011</t>
-  </si>
-  <si>
-    <t>0.3765,0.6494,0.1024,0.0020</t>
-  </si>
-  <si>
-    <t>0.1867,0.8432,0.0863,0.0006</t>
-  </si>
-  <si>
-    <t>0.9029,0.0176,0.0823,0.0006</t>
-  </si>
-  <si>
-    <t>0.9835,0.0034,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.9115,0.0101,0.0860,0.0002</t>
-  </si>
-  <si>
-    <t>0.9506,0.0051,0.0414,0.0002</t>
-  </si>
-  <si>
-    <t>0.9257,0.0080,0.0951,0.0002</t>
-  </si>
-  <si>
-    <t>0.7905,0.0508,0.1258,0.0004</t>
-  </si>
-  <si>
-    <t>0.6719,0.0075,0.4861,0.0014</t>
-  </si>
-  <si>
-    <t>0.5649,0.3369,0.1946,0.0039</t>
-  </si>
-  <si>
-    <t>0.7494,0.1506,0.1016,0.0032</t>
-  </si>
-  <si>
-    <t>0.0968,0.0442,0.9482,0.0024</t>
-  </si>
-  <si>
-    <t>0.6840,0.2185,0.1312,0.0021</t>
-  </si>
-  <si>
-    <t>0.8562,0.0714,0.0573,0.0016</t>
-  </si>
-  <si>
-    <t>0.7853,0.1107,0.0792,0.0067</t>
-  </si>
-  <si>
-    <t>0.8095,0.1132,0.0632,0.0046</t>
-  </si>
-  <si>
-    <t>0.8422,0.1309,0.0513,0.0008</t>
-  </si>
-  <si>
-    <t>0.5054,0.4845,0.0154,0.0007</t>
-  </si>
-  <si>
-    <t>0.9043,0.0011,0.1234,0.0002</t>
-  </si>
-  <si>
-    <t>0.9626,0.0021,0.0408,0.0001</t>
-  </si>
-  <si>
-    <t>0.9271,0.0036,0.0724,0.0002</t>
-  </si>
-  <si>
-    <t>0.9644,0.0039,0.0327,0.0001</t>
-  </si>
-  <si>
-    <t>0.3519,0.4715,0.1341,0.0008</t>
-  </si>
-  <si>
-    <t>0.9115,0.0024,0.0932,0.0006</t>
-  </si>
-  <si>
-    <t>0.9318,0.0317,0.0219,0.0010</t>
-  </si>
-  <si>
-    <t>0.7499,0.3003,0.0445,0.0008</t>
-  </si>
-  <si>
-    <t>0.2495,0.8052,0.0471,0.0001</t>
-  </si>
-  <si>
-    <t>0.7217,0.3167,0.0599,0.0005</t>
-  </si>
-  <si>
-    <t>0.1828,0.0545,0.8357,0.0005</t>
-  </si>
-  <si>
-    <t>0.7715,0.0063,0.3909,0.0004</t>
-  </si>
-  <si>
-    <t>0.9019,0.0084,0.1092,0.0002</t>
-  </si>
-  <si>
-    <t>0.8054,0.0051,0.3302,0.0001</t>
-  </si>
-  <si>
-    <t>0.7774,0.0102,0.3252,0.0002</t>
-  </si>
-  <si>
-    <t>0.9171,0.0032,0.1223,0.0001</t>
-  </si>
-  <si>
-    <t>0.6711,0.2470,0.0708,0.0125</t>
-  </si>
-  <si>
-    <t>0.8515,0.0554,0.0390,0.0049</t>
-  </si>
-  <si>
-    <t>0.7445,0.1001,0.0674,0.0157</t>
-  </si>
-  <si>
-    <t>0.2426,0.0984,0.8400,0.0034</t>
-  </si>
-  <si>
-    <t>0.8098,0.0615,0.0329,0.0153</t>
-  </si>
-  <si>
-    <t>0.8680,0.0306,0.0462,0.0067</t>
-  </si>
-  <si>
-    <t>0.7473,0.1203,0.1148,0.0100</t>
-  </si>
-  <si>
-    <t>0.2895,0.2794,0.4308,0.0014</t>
-  </si>
-  <si>
-    <t>0.8277,0.0053,0.2828,0.0001</t>
-  </si>
-  <si>
-    <t>0.9033,0.0027,0.1277,0.0001</t>
-  </si>
-  <si>
-    <t>0.2801,0.4159,0.2686,0.0002</t>
-  </si>
-  <si>
-    <t>0.6636,0.0046,0.5616,0.0002</t>
-  </si>
-  <si>
-    <t>0.9372,0.0482,0.0153,0.0003</t>
-  </si>
-  <si>
-    <t>0.0157,0.9884,0.0161,0.0001</t>
-  </si>
-  <si>
-    <t>0.9510,0.0284,0.0133,0.0006</t>
-  </si>
-  <si>
-    <t>0.8518,0.1213,0.0491,0.0008</t>
-  </si>
-  <si>
-    <t>0.1522,0.2007,0.8476,0.0008</t>
-  </si>
-  <si>
-    <t>0.9364,0.0166,0.0377,0.0001</t>
-  </si>
-  <si>
-    <t>0.9426,0.0223,0.0256,0.0001</t>
-  </si>
-  <si>
-    <t>0.1352,0.8580,0.0272,0.0001</t>
-  </si>
-  <si>
-    <t>0.2650,0.3161,0.2479,0.0002</t>
-  </si>
-  <si>
-    <t>0.9664,0.0077,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.8556,0.0464,0.0499,0.0055</t>
-  </si>
-  <si>
-    <t>0.9276,0.0336,0.0142,0.0025</t>
-  </si>
-  <si>
-    <t>0.9572,0.0247,0.0111,0.0005</t>
-  </si>
-  <si>
-    <t>0.8484,0.0491,0.0692,0.0045</t>
-  </si>
-  <si>
-    <t>0.9571,0.0092,0.0163,0.0008</t>
-  </si>
-  <si>
-    <t>0.7364,0.0623,0.1183,0.0001</t>
-  </si>
-  <si>
-    <t>0.7659,0.0152,0.2477,0.0001</t>
-  </si>
-  <si>
-    <t>0.9038,0.0181,0.0552,0.0001</t>
-  </si>
-  <si>
-    <t>0.7212,0.0427,0.2078,0.0006</t>
-  </si>
-  <si>
-    <t>0.5970,0.2847,0.1057,0.0002</t>
-  </si>
-  <si>
-    <t>0.8983,0.0128,0.0987,0.0003</t>
-  </si>
-  <si>
-    <t>0.6389,0.2809,0.1124,0.0115</t>
-  </si>
-  <si>
-    <t>0.7913,0.0556,0.0510,0.0157</t>
-  </si>
-  <si>
-    <t>0.8424,0.0674,0.0393,0.0071</t>
-  </si>
-  <si>
-    <t>0.7831,0.0784,0.0372,0.0162</t>
-  </si>
-  <si>
-    <t>0.8317,0.0636,0.0614,0.0040</t>
-  </si>
-  <si>
-    <t>0.8116,0.0376,0.0574,0.0227</t>
-  </si>
-  <si>
-    <t>0.8365,0.0279,0.0239,0.0254</t>
-  </si>
-  <si>
-    <t>0.7973,0.0528,0.0640,0.0155</t>
-  </si>
-  <si>
-    <t>0.6801,0.1450,0.0477,0.0203</t>
-  </si>
-  <si>
-    <t>0.9253,0.0162,0.0091,0.0068</t>
-  </si>
-  <si>
-    <t>0.7434,0.0997,0.0353,0.0247</t>
-  </si>
-  <si>
-    <t>0.8419,0.0387,0.0211,0.0211</t>
-  </si>
-  <si>
-    <t>0.7368,0.1282,0.0468,0.0143</t>
-  </si>
-  <si>
-    <t>0.7730,0.0735,0.0494,0.0242</t>
-  </si>
-  <si>
-    <t>0.6411,0.3001,0.1067,0.0072</t>
-  </si>
-  <si>
-    <t>0.8948,0.0214,0.0120,0.0115</t>
-  </si>
-  <si>
-    <t>0.2638,0.0174,0.8473,0.0006</t>
-  </si>
-  <si>
-    <t>0.6913,0.0255,0.4239,0.0016</t>
-  </si>
-  <si>
-    <t>0.9638,0.0058,0.0223,0.0005</t>
-  </si>
-  <si>
-    <t>0.9171,0.0050,0.1214,0.0002</t>
-  </si>
-  <si>
-    <t>0.7225,0.2739,0.0596,0.0011</t>
-  </si>
-  <si>
-    <t>0.6007,0.3387,0.1178,0.0024</t>
-  </si>
-  <si>
-    <t>0.4583,0.5669,0.0920,0.0039</t>
-  </si>
-  <si>
-    <t>0.7795,0.1744,0.0437,0.0041</t>
-  </si>
-  <si>
-    <t>0.2415,0.7906,0.1605,0.0028</t>
-  </si>
-  <si>
-    <t>0.4069,0.6402,0.1084,0.0005</t>
-  </si>
-  <si>
-    <t>0.7248,0.1978,0.1037,0.0036</t>
-  </si>
-  <si>
-    <t>0.9628,0.0072,0.0191,0.0003</t>
-  </si>
-  <si>
-    <t>0.9431,0.0049,0.0688,0.0001</t>
-  </si>
-  <si>
-    <t>0.9596,0.0121,0.0174,0.0002</t>
-  </si>
-  <si>
-    <t>0.9615,0.0136,0.0146,0.0002</t>
-  </si>
-  <si>
-    <t>0.8617,0.0756,0.0651,0.0010</t>
-  </si>
-  <si>
-    <t>0.4912,0.5709,0.0703,0.0005</t>
-  </si>
-  <si>
-    <t>0.2224,0.8636,0.0300,0.0021</t>
-  </si>
-  <si>
-    <t>0.8339,0.1448,0.0365,0.0009</t>
-  </si>
-  <si>
-    <t>0.2895,0.6849,0.1763,0.0014</t>
-  </si>
-  <si>
-    <t>0.8124,0.1489,0.0578,0.0012</t>
-  </si>
-  <si>
-    <t>0.8419,0.0669,0.0681,0.0031</t>
-  </si>
-  <si>
-    <t>0.7542,0.1593,0.0888,0.0033</t>
-  </si>
-  <si>
-    <t>0.8164,0.0559,0.0328,0.0174</t>
-  </si>
-  <si>
-    <t>0.6881,0.2034,0.0993,0.0077</t>
-  </si>
-  <si>
-    <t>0.7015,0.1415,0.0814,0.0161</t>
-  </si>
-  <si>
-    <t>0.8737,0.0315,0.0411,0.0072</t>
-  </si>
-  <si>
-    <t>0.8831,0.0419,0.0358,0.0061</t>
-  </si>
-  <si>
-    <t>0.8760,0.0468,0.0420,0.0037</t>
-  </si>
-  <si>
-    <t>0.8418,0.0460,0.0488,0.0096</t>
-  </si>
-  <si>
-    <t>0.7756,0.0826,0.0641,0.0118</t>
-  </si>
-  <si>
-    <t>0.8453,0.0098,0.2488,0.0002</t>
-  </si>
-  <si>
-    <t>0.7727,0.1267,0.0619,0.0003</t>
-  </si>
-  <si>
-    <t>0.8898,0.0040,0.1381,0.0001</t>
-  </si>
-  <si>
-    <t>0.8928,0.0068,0.1179,0.0001</t>
-  </si>
-  <si>
-    <t>0.9644,0.0129,0.0118,0.0003</t>
-  </si>
-  <si>
-    <t>0.9463,0.0123,0.0405,0.0002</t>
-  </si>
-  <si>
-    <t>0.9193,0.0125,0.0805,0.0002</t>
-  </si>
-  <si>
-    <t>0.9365,0.0353,0.0185,0.0002</t>
-  </si>
-  <si>
-    <t>0.9514,0.0071,0.0233,0.0010</t>
-  </si>
-  <si>
-    <t>0.8968,0.0192,0.0302,0.0071</t>
-  </si>
-  <si>
-    <t>0.9398,0.0225,0.0185,0.0014</t>
-  </si>
-  <si>
-    <t>0.9042,0.0278,0.0337,0.0045</t>
-  </si>
-  <si>
-    <t>0.6008,0.3467,0.0629,0.0010</t>
-  </si>
-  <si>
-    <t>0.8020,0.0901,0.0772,0.0072</t>
-  </si>
-  <si>
-    <t>0.8119,0.1200,0.0578,0.0017</t>
-  </si>
-  <si>
-    <t>0.8091,0.0719,0.0501,0.0107</t>
-  </si>
-  <si>
-    <t>0.8083,0.1350,0.0643,0.0042</t>
-  </si>
-  <si>
-    <t>0.8597,0.0392,0.0678,0.0024</t>
-  </si>
-  <si>
-    <t>0.9316,0.0311,0.0185,0.0011</t>
-  </si>
-  <si>
-    <t>0.7841,0.0810,0.0542,0.0145</t>
-  </si>
-  <si>
-    <t>0.3810,0.1565,0.5629,0.0129</t>
-  </si>
-  <si>
-    <t>0.8049,0.1048,0.0462,0.0099</t>
-  </si>
-  <si>
-    <t>0.7263,0.1695,0.0617,0.0116</t>
-  </si>
-  <si>
-    <t>0.8102,0.1023,0.0964,0.0010</t>
-  </si>
-  <si>
-    <t>0.8978,0.0254,0.0520,0.0023</t>
-  </si>
-  <si>
-    <t>0.9241,0.0427,0.0271,0.0007</t>
-  </si>
-  <si>
-    <t>0.8472,0.0802,0.0449,0.0043</t>
-  </si>
-  <si>
-    <t>0.8538,0.1288,0.0336,0.0010</t>
-  </si>
-  <si>
-    <t>0.9267,0.0349,0.0244,0.0009</t>
-  </si>
-  <si>
-    <t>0.7589,0.1090,0.0802,0.0109</t>
-  </si>
-  <si>
-    <t>0.7548,0.1185,0.0639,0.0095</t>
-  </si>
-  <si>
-    <t>0.7997,0.0805,0.0621,0.0157</t>
-  </si>
-  <si>
-    <t>0.7593,0.1345,0.0751,0.0064</t>
-  </si>
-  <si>
-    <t>0.7616,0.0887,0.0564,0.0150</t>
-  </si>
-  <si>
-    <t>0.8204,0.0909,0.0341,0.0047</t>
-  </si>
-  <si>
-    <t>0.7396,0.0872,0.0722,0.0172</t>
-  </si>
-  <si>
-    <t>0.8856,0.0601,0.0272,0.0021</t>
-  </si>
-  <si>
-    <t>0.5048,0.4735,0.0947,0.0082</t>
-  </si>
-  <si>
-    <t>0.8616,0.1074,0.0401,0.0013</t>
-  </si>
-  <si>
-    <t>0.8061,0.1037,0.0859,0.0054</t>
-  </si>
-  <si>
-    <t>0.5185,0.3678,0.1739,0.0108</t>
-  </si>
-  <si>
-    <t>0.7334,0.2052,0.1116,0.0025</t>
-  </si>
-  <si>
-    <t>0.8889,0.0351,0.0394,0.0044</t>
-  </si>
-  <si>
-    <t>0.6846,0.1904,0.1025,0.0129</t>
-  </si>
-  <si>
-    <t>0.7055,0.1758,0.1372,0.0024</t>
-  </si>
-  <si>
-    <t>0.0981,0.0542,0.9443,0.0005</t>
-  </si>
-  <si>
-    <t>0.7782,0.1678,0.0333,0.0032</t>
-  </si>
-  <si>
-    <t>0.9118,0.0058,0.0703,0.0000</t>
-  </si>
-  <si>
-    <t>0.9518,0.0015,0.0565,0.0001</t>
-  </si>
-  <si>
-    <t>0.7950,0.0344,0.1897,0.0005</t>
-  </si>
-  <si>
-    <t>0.7637,0.0624,0.1348,0.0007</t>
-  </si>
-  <si>
-    <t>0.9524,0.0011,0.0757,0.0000</t>
-  </si>
-  <si>
-    <t>0.9183,0.0008,0.1549,0.0000</t>
-  </si>
-  <si>
-    <t>0.9129,0.0032,0.1345,0.0001</t>
-  </si>
-  <si>
-    <t>0.9384,0.0130,0.0467,0.0001</t>
-  </si>
-  <si>
-    <t>0.9449,0.0211,0.0255,0.0002</t>
-  </si>
-  <si>
-    <t>0.9279,0.0390,0.0241,0.0003</t>
-  </si>
-  <si>
-    <t>0.7635,0.1356,0.1211,0.0008</t>
-  </si>
-  <si>
-    <t>0.8706,0.0561,0.0673,0.0003</t>
-  </si>
-  <si>
-    <t>0.9328,0.0271,0.0315,0.0003</t>
-  </si>
-  <si>
-    <t>0.9389,0.0174,0.0281,0.0009</t>
-  </si>
-  <si>
-    <t>0.8674,0.1014,0.0397,0.0014</t>
-  </si>
-  <si>
-    <t>0.6142,0.3223,0.0912,0.0056</t>
-  </si>
-  <si>
-    <t>0.6585,0.2527,0.0765,0.0069</t>
-  </si>
-  <si>
-    <t>0.7217,0.1382,0.0684,0.0125</t>
-  </si>
-  <si>
-    <t>0.7198,0.1518,0.0391,0.0115</t>
-  </si>
-  <si>
-    <t>0.7793,0.0910,0.0434,0.0133</t>
-  </si>
-  <si>
-    <t>0.9130,0.0505,0.0263,0.0005</t>
-  </si>
-  <si>
-    <t>0.8070,0.0351,0.1779,0.0029</t>
-  </si>
-  <si>
-    <t>0.9128,0.0225,0.0512,0.0005</t>
-  </si>
-  <si>
-    <t>0.9474,0.0206,0.0217,0.0004</t>
-  </si>
-  <si>
-    <t>0.9071,0.0293,0.0499,0.0010</t>
-  </si>
-  <si>
-    <t>0.8338,0.0227,0.1451,0.0004</t>
-  </si>
-  <si>
-    <t>0.8253,0.0687,0.0585,0.0003</t>
-  </si>
-  <si>
-    <t>0.8956,0.0057,0.1171,0.0005</t>
-  </si>
-  <si>
-    <t>0.9495,0.0011,0.0663,0.0001</t>
-  </si>
-  <si>
-    <t>0.8810,0.0227,0.0747,0.0003</t>
-  </si>
-  <si>
-    <t>0.6436,0.2216,0.0539,0.0148</t>
-  </si>
-  <si>
-    <t>0.7670,0.1412,0.0454,0.0062</t>
-  </si>
-  <si>
-    <t>0.7573,0.0993,0.0493,0.0170</t>
-  </si>
-  <si>
-    <t>0.8310,0.0678,0.0498,0.0089</t>
-  </si>
-  <si>
-    <t>0.7108,0.1584,0.0988,0.0123</t>
-  </si>
-  <si>
-    <t>0.5784,0.2902,0.0608,0.0147</t>
-  </si>
-  <si>
-    <t>0.6462,0.2234,0.0823,0.0090</t>
-  </si>
-  <si>
-    <t>0.5763,0.2055,0.0430,0.0261</t>
-  </si>
-  <si>
-    <t>0.8403,0.0259,0.1683,0.0008</t>
-  </si>
-  <si>
-    <t>0.8642,0.0720,0.0586,0.0009</t>
-  </si>
-  <si>
-    <t>0.6432,0.2639,0.1072,0.0071</t>
-  </si>
-  <si>
-    <t>0.1830,0.0363,0.8994,0.0003</t>
-  </si>
-  <si>
-    <t>0.5931,0.0086,0.5413,0.0007</t>
-  </si>
-  <si>
-    <t>0.8216,0.0389,0.1693,0.0006</t>
-  </si>
-  <si>
-    <t>0.3495,0.0071,0.8186,0.0001</t>
-  </si>
-  <si>
-    <t>0.7470,0.0458,0.2193,0.0001</t>
-  </si>
-  <si>
-    <t>0.1849,0.0264,0.8947,0.0005</t>
-  </si>
-  <si>
-    <t>0.9444,0.0056,0.0404,0.0002</t>
-  </si>
-  <si>
-    <t>0.8270,0.0380,0.1719,0.0007</t>
-  </si>
-  <si>
-    <t>0.8003,0.1297,0.0649,0.0029</t>
-  </si>
-  <si>
-    <t>0.9645,0.0051,0.0203,0.0002</t>
-  </si>
-  <si>
-    <t>0.9687,0.0115,0.0118,0.0001</t>
-  </si>
-  <si>
-    <t>0.6489,0.1437,0.0829,0.0272</t>
-  </si>
-  <si>
-    <t>0.8615,0.0742,0.0403,0.0037</t>
-  </si>
-  <si>
-    <t>0.8386,0.0392,0.0252,0.0093</t>
-  </si>
-  <si>
-    <t>0.8597,0.0764,0.0485,0.0028</t>
-  </si>
-  <si>
-    <t>0.5921,0.1084,0.0369,0.0453</t>
-  </si>
-  <si>
-    <t>0.7219,0.1026,0.0534,0.0172</t>
-  </si>
-  <si>
-    <t>0.7356,0.1076,0.1109,0.0147</t>
-  </si>
-  <si>
-    <t>0.7665,0.1231,0.0692,0.0090</t>
-  </si>
-  <si>
-    <t>0.7711,0.0304,0.2294,0.0004</t>
-  </si>
-  <si>
-    <t>0.0476,0.8949,0.2827,0.0002</t>
-  </si>
-  <si>
-    <t>0.9146,0.0115,0.0645,0.0002</t>
-  </si>
-  <si>
-    <t>0.9482,0.0076,0.0339,0.0002</t>
-  </si>
-  <si>
-    <t>0.9112,0.0028,0.1343,0.0001</t>
-  </si>
-  <si>
-    <t>0.8956,0.0119,0.0958,0.0004</t>
-  </si>
-  <si>
-    <t>0.9080,0.0088,0.0921,0.0005</t>
-  </si>
-  <si>
-    <t>0.9321,0.0088,0.0532,0.0003</t>
-  </si>
-  <si>
-    <t>0.8969,0.0555,0.0297,0.0021</t>
-  </si>
-  <si>
-    <t>0.9513,0.0248,0.0101,0.0009</t>
-  </si>
-  <si>
-    <t>0.9104,0.0464,0.0234,0.0034</t>
-  </si>
-  <si>
-    <t>0.9570,0.0063,0.0197,0.0006</t>
-  </si>
-  <si>
-    <t>0.8912,0.0147,0.0107,0.0155</t>
-  </si>
-  <si>
-    <t>0.8757,0.0540,0.0469,0.0026</t>
+    <t>0.9453,0.0213,0.0164,0.0075</t>
+  </si>
+  <si>
+    <t>0.1535,0.0003,0.0009,0.9424</t>
+  </si>
+  <si>
+    <t>0.9713,0.0020,0.0025,0.0154</t>
+  </si>
+  <si>
+    <t>0.0335,0.0028,0.0139,0.9770</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0010,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0023,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.6204,0.0751,0.3618,0.0033</t>
+  </si>
+  <si>
+    <t>0.0528,0.0054,0.9674,0.0041</t>
+  </si>
+  <si>
+    <t>0.4499,0.0077,0.7619,0.0006</t>
+  </si>
+  <si>
+    <t>0.0201,0.0092,0.9697,0.0042</t>
+  </si>
+  <si>
+    <t>0.9368,0.0049,0.0247,0.0104</t>
+  </si>
+  <si>
+    <t>0.0019,0.9967,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9962,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.1408,0.8854,0.0059,0.0011</t>
+  </si>
+  <si>
+    <t>0.0137,0.9814,0.0058,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.9974,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.7346,0.0104,0.2745,0.0149</t>
+  </si>
+  <si>
+    <t>0.5321,0.0323,0.5301,0.0128</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9972,0.0022</t>
+  </si>
+  <si>
+    <t>0.1290,0.0240,0.8936,0.0106</t>
+  </si>
+  <si>
+    <t>0.4219,0.0019,0.7481,0.0013</t>
+  </si>
+  <si>
+    <t>0.0078,0.0010,0.9919,0.0048</t>
+  </si>
+  <si>
+    <t>0.0011,0.0017,0.9929,0.0133</t>
+  </si>
+  <si>
+    <t>0.8140,0.2872,0.0072,0.0030</t>
+  </si>
+  <si>
+    <t>0.6692,0.0643,0.3049,0.0245</t>
+  </si>
+  <si>
+    <t>0.0015,0.0033,0.9968,0.0022</t>
+  </si>
+  <si>
+    <t>0.0053,0.9038,0.2960,0.0003</t>
+  </si>
+  <si>
+    <t>0.7275,0.0380,0.0345,0.2039</t>
+  </si>
+  <si>
+    <t>0.8071,0.0554,0.1008,0.0421</t>
+  </si>
+  <si>
+    <t>0.5649,0.5450,0.0147,0.0022</t>
+  </si>
+  <si>
+    <t>0.0092,0.9733,0.4350,0.0010</t>
+  </si>
+  <si>
+    <t>0.0294,0.8842,0.1091,0.0809</t>
+  </si>
+  <si>
+    <t>0.0212,0.0019,0.9864,0.0018</t>
+  </si>
+  <si>
+    <t>0.0414,0.0104,0.9682,0.0049</t>
+  </si>
+  <si>
+    <t>0.6250,0.0059,0.3982,0.0150</t>
+  </si>
+  <si>
+    <t>0.0090,0.0932,0.9648,0.0025</t>
+  </si>
+  <si>
+    <t>0.0178,0.8347,0.2013,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.0069,0.9917,0.0012</t>
+  </si>
+  <si>
+    <t>0.3670,0.2802,0.0077,0.3757</t>
+  </si>
+  <si>
+    <t>0.0175,0.9332,0.0092,0.0564</t>
+  </si>
+  <si>
+    <t>0.0006,0.9954,0.0302,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.9969,0.0158,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0821,0.9911,0.0025</t>
+  </si>
+  <si>
+    <t>0.0135,0.5309,0.9432,0.0048</t>
+  </si>
+  <si>
+    <t>0.0517,0.0239,0.9524,0.0034</t>
+  </si>
+  <si>
+    <t>0.0730,0.0059,0.9511,0.0063</t>
+  </si>
+  <si>
+    <t>0.0105,0.0123,0.9796,0.0110</t>
+  </si>
+  <si>
+    <t>0.0330,0.4364,0.7914,0.0097</t>
+  </si>
+  <si>
+    <t>0.9555,0.0550,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.9811,0.0092,0.0056,0.0016</t>
+  </si>
+  <si>
+    <t>0.9805,0.0133,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.0443,0.0868,0.9442,0.0290</t>
+  </si>
+  <si>
+    <t>0.9880,0.0053,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9848,0.0098,0.0009,0.0023</t>
+  </si>
+  <si>
+    <t>0.9709,0.0294,0.0035,0.0018</t>
+  </si>
+  <si>
+    <t>0.0031,0.5506,0.9844,0.0008</t>
+  </si>
+  <si>
+    <t>0.0048,0.1643,0.9764,0.0044</t>
+  </si>
+  <si>
+    <t>0.0056,0.2602,0.9420,0.0129</t>
+  </si>
+  <si>
+    <t>0.0002,0.9878,0.9710,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0037,0.9953,0.0029</t>
+  </si>
+  <si>
+    <t>0.0541,0.9427,0.0062,0.0007</t>
+  </si>
+  <si>
+    <t>0.0204,0.9745,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.2480,0.0216,0.8475,0.0250</t>
+  </si>
+  <si>
+    <t>0.0622,0.0838,0.9467,0.0041</t>
+  </si>
+  <si>
+    <t>0.0101,0.0198,0.9818,0.0039</t>
+  </si>
+  <si>
+    <t>0.0020,0.9570,0.6999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0091,0.7742,0.8073,0.0006</t>
+  </si>
+  <si>
+    <t>0.0118,0.9780,0.0113,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.9626,0.9503,0.0004</t>
+  </si>
+  <si>
+    <t>0.0241,0.0051,0.0946,0.9373</t>
+  </si>
+  <si>
+    <t>0.0014,0.0032,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0022,0.0024,0.0021,0.9978</t>
+  </si>
+  <si>
+    <t>0.0140,0.0025,0.0257,0.9791</t>
+  </si>
+  <si>
+    <t>0.0040,0.0091,0.0028,0.9940</t>
+  </si>
+  <si>
+    <t>0.0013,0.0079,0.0009,0.9980</t>
+  </si>
+  <si>
+    <t>0.0006,0.9825,0.8805,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.1462,0.9868,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.5188,0.8477,0.0012</t>
+  </si>
+  <si>
+    <t>0.0053,0.2361,0.9677,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.9970,0.9076,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9809,0.0958,0.0009</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9836,0.0202,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9664,0.0268,0.0020,0.0035</t>
+  </si>
+  <si>
+    <t>0.9956,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0038,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9930,0.0026,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9892,0.0098,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0018,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9954,0.0009,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0016,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9935,0.0031,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.0018,0.9825,0.0193</t>
+  </si>
+  <si>
+    <t>0.0053,0.0121,0.9922,0.0018</t>
+  </si>
+  <si>
+    <t>0.9614,0.0031,0.0232,0.0029</t>
+  </si>
+  <si>
+    <t>0.0112,0.0026,0.9924,0.0011</t>
+  </si>
+  <si>
+    <t>0.0181,0.9756,0.0024,0.0020</t>
+  </si>
+  <si>
+    <t>0.0056,0.9884,0.0091,0.0023</t>
+  </si>
+  <si>
+    <t>0.0695,0.9277,0.0076,0.0021</t>
+  </si>
+  <si>
+    <t>0.0021,0.9954,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.0023,0.9944,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.9968,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.1292,0.8798,0.0113,0.0037</t>
+  </si>
+  <si>
+    <t>0.2122,0.6300,0.1182,0.1109</t>
+  </si>
+  <si>
+    <t>0.2698,0.0083,0.8546,0.0031</t>
+  </si>
+  <si>
+    <t>0.4970,0.0783,0.4327,0.0497</t>
+  </si>
+  <si>
+    <t>0.5492,0.0519,0.3807,0.0200</t>
+  </si>
+  <si>
+    <t>0.4118,0.4202,0.0858,0.1385</t>
+  </si>
+  <si>
+    <t>0.0058,0.9867,0.0454,0.0017</t>
+  </si>
+  <si>
+    <t>0.0038,0.9905,0.0109,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.9956,0.0019,0.0335</t>
+  </si>
+  <si>
+    <t>0.0010,0.9730,0.8501,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.9914,0.0242,0.0003</t>
+  </si>
+  <si>
+    <t>0.7957,0.1657,0.0532,0.0060</t>
+  </si>
+  <si>
+    <t>0.9629,0.0367,0.0052,0.0025</t>
+  </si>
+  <si>
+    <t>0.9932,0.0025,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9903,0.0018,0.0016,0.0029</t>
+  </si>
+  <si>
+    <t>0.9850,0.0045,0.0027,0.0038</t>
+  </si>
+  <si>
+    <t>0.9595,0.0055,0.0264,0.0040</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0001,0.0049</t>
+  </si>
+  <si>
+    <t>0.9901,0.0045,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9944,0.0006,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.8564,0.8856,0.0008</t>
+  </si>
+  <si>
+    <t>0.0066,0.3610,0.9611,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.0164,0.9913,0.0008</t>
+  </si>
+  <si>
+    <t>0.0048,0.0110,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.9913,0.0009,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.7465,0.0110,0.2512,0.0219</t>
+  </si>
+  <si>
+    <t>0.0764,0.0021,0.9709,0.0033</t>
+  </si>
+  <si>
+    <t>0.7446,0.0096,0.3100,0.0063</t>
+  </si>
+  <si>
+    <t>0.0032,0.0008,0.0014,0.9980</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0043,0.0017,0.9986</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.0055,0.9981</t>
+  </si>
+  <si>
+    <t>0.0028,0.1812,0.9696,0.0043</t>
+  </si>
+  <si>
+    <t>0.9841,0.0019,0.0027,0.0056</t>
+  </si>
+  <si>
+    <t>0.1348,0.8861,0.0055,0.0066</t>
+  </si>
+  <si>
+    <t>0.9770,0.0127,0.0044,0.0040</t>
+  </si>
+  <si>
+    <t>0.9174,0.1235,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.9949,0.0010,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.2662,0.0150,0.0373,0.7906</t>
+  </si>
+  <si>
+    <t>0.9866,0.0019,0.0025,0.0032</t>
+  </si>
+  <si>
+    <t>0.0076,0.1965,0.9045,0.0857</t>
+  </si>
+  <si>
+    <t>0.9811,0.0007,0.0008,0.0129</t>
+  </si>
+  <si>
+    <t>0.9102,0.0034,0.0045,0.0699</t>
+  </si>
+  <si>
+    <t>0.2182,0.7856,0.0058,0.0077</t>
+  </si>
+  <si>
+    <t>0.8745,0.1106,0.0056,0.0115</t>
+  </si>
+  <si>
+    <t>0.9455,0.0375,0.0100,0.0036</t>
+  </si>
+  <si>
+    <t>0.2589,0.6307,0.1270,0.0592</t>
+  </si>
+  <si>
+    <t>0.8059,0.2196,0.0277,0.0038</t>
+  </si>
+  <si>
+    <t>0.8887,0.1082,0.0232,0.0049</t>
+  </si>
+  <si>
+    <t>0.9832,0.0032,0.0054,0.0030</t>
+  </si>
+  <si>
+    <t>0.9908,0.0015,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9927,0.0004,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9924,0.0005,0.0003,0.0047</t>
+  </si>
+  <si>
+    <t>0.9928,0.0036,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9756,0.0169,0.0045,0.0023</t>
+  </si>
+  <si>
+    <t>0.9939,0.0008,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.8391,0.1619,0.0101,0.0062</t>
+  </si>
+  <si>
+    <t>0.7603,0.3103,0.0057,0.0016</t>
+  </si>
+  <si>
+    <t>0.6225,0.4309,0.0145,0.0035</t>
+  </si>
+  <si>
+    <t>0.0495,0.0495,0.9701,0.0041</t>
+  </si>
+  <si>
+    <t>0.9832,0.0151,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9822,0.0168,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9739,0.0178,0.0009,0.0026</t>
+  </si>
+  <si>
+    <t>0.9664,0.0216,0.0020,0.0070</t>
+  </si>
+  <si>
+    <t>0.0039,0.0020,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.8921,0.1384,0.0126,0.0073</t>
+  </si>
+  <si>
+    <t>0.0035,0.0044,0.9927,0.0028</t>
+  </si>
+  <si>
+    <t>0.0045,0.0024,0.9932,0.0033</t>
+  </si>
+  <si>
+    <t>0.0266,0.0011,0.9889,0.0015</t>
+  </si>
+  <si>
+    <t>0.0053,0.0385,0.9895,0.0017</t>
+  </si>
+  <si>
+    <t>0.0159,0.0030,0.9896,0.0009</t>
+  </si>
+  <si>
+    <t>0.0174,0.0016,0.9887,0.0009</t>
+  </si>
+  <si>
+    <t>0.0051,0.0038,0.9940,0.0023</t>
+  </si>
+  <si>
+    <t>0.1986,0.0658,0.7900,0.0241</t>
+  </si>
+  <si>
+    <t>0.4101,0.1307,0.4926,0.0208</t>
+  </si>
+  <si>
+    <t>0.2938,0.0034,0.8597,0.0022</t>
+  </si>
+  <si>
+    <t>0.4311,0.0249,0.6713,0.0063</t>
+  </si>
+  <si>
+    <t>0.0553,0.0805,0.8969,0.0015</t>
+  </si>
+  <si>
+    <t>0.5854,0.0965,0.2516,0.0029</t>
+  </si>
+  <si>
+    <t>0.7972,0.0303,0.1852,0.0071</t>
+  </si>
+  <si>
+    <t>0.1735,0.0320,0.8603,0.0173</t>
+  </si>
+  <si>
+    <t>0.0750,0.9387,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.0666,0.9469,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.6323,0.5265,0.0034,0.0013</t>
+  </si>
+  <si>
+    <t>0.9739,0.0240,0.0040,0.0012</t>
+  </si>
+  <si>
+    <t>0.1872,0.8619,0.0033,0.0025</t>
+  </si>
+  <si>
+    <t>0.8858,0.0115,0.0524,0.0213</t>
+  </si>
+  <si>
+    <t>0.9550,0.0034,0.0244,0.0033</t>
+  </si>
+  <si>
+    <t>0.5971,0.0125,0.2268,0.0895</t>
+  </si>
+  <si>
+    <t>0.9351,0.0098,0.0496,0.0021</t>
+  </si>
+  <si>
+    <t>0.5369,0.0316,0.4252,0.0148</t>
+  </si>
+  <si>
+    <t>0.0269,0.0169,0.9590,0.0180</t>
+  </si>
+  <si>
+    <t>0.0545,0.0961,0.7831,0.1316</t>
+  </si>
+  <si>
+    <t>0.4429,0.0115,0.5309,0.0438</t>
+  </si>
+  <si>
+    <t>0.0171,0.0064,0.9761,0.0040</t>
+  </si>
+  <si>
+    <t>0.0234,0.0128,0.9742,0.0031</t>
+  </si>
+  <si>
+    <t>0.9909,0.0016,0.0004,0.0034</t>
+  </si>
+  <si>
+    <t>0.9839,0.0036,0.0020,0.0058</t>
+  </si>
+  <si>
+    <t>0.9771,0.0146,0.0021,0.0033</t>
+  </si>
+  <si>
+    <t>0.9910,0.0077,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9883,0.0053,0.0009,0.0025</t>
+  </si>
+  <si>
+    <t>0.9782,0.0130,0.0042,0.0047</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0268,0.0152,0.9763,0.0111</t>
+  </si>
+  <si>
+    <t>0.6450,0.2077,0.1596,0.0119</t>
+  </si>
+  <si>
+    <t>0.8650,0.0757,0.0424,0.0041</t>
+  </si>
+  <si>
+    <t>0.0169,0.0010,0.9889,0.0021</t>
+  </si>
+  <si>
+    <t>0.0091,0.0116,0.9782,0.0116</t>
+  </si>
+  <si>
+    <t>0.1118,0.1127,0.8306,0.0230</t>
+  </si>
+  <si>
+    <t>0.0049,0.0035,0.9953,0.0012</t>
+  </si>
+  <si>
+    <t>0.0116,0.0028,0.9892,0.0033</t>
+  </si>
+  <si>
+    <t>0.0009,0.0013,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9967,0.0043</t>
+  </si>
+  <si>
+    <t>0.1410,0.0220,0.8473,0.0063</t>
+  </si>
+  <si>
+    <t>0.6548,0.0120,0.2998,0.0493</t>
+  </si>
+  <si>
+    <t>0.8410,0.0055,0.1739,0.0053</t>
+  </si>
+  <si>
+    <t>0.9651,0.0031,0.0210,0.0016</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9883,0.0098,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9964,0.0004,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9889,0.0093,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9932,0.0050,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0035,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.0433,0.0536,0.9350,0.0037</t>
+  </si>
+  <si>
+    <t>0.0092,0.0538,0.9789,0.0019</t>
+  </si>
+  <si>
+    <t>0.0094,0.0157,0.9734,0.0123</t>
+  </si>
+  <si>
+    <t>0.0242,0.0071,0.9724,0.0064</t>
+  </si>
+  <si>
+    <t>0.0073,0.0086,0.9909,0.0013</t>
+  </si>
+  <si>
+    <t>0.1324,0.0024,0.3603,0.3984</t>
+  </si>
+  <si>
+    <t>0.0243,0.0140,0.9780,0.0049</t>
+  </si>
+  <si>
+    <t>0.2608,0.0130,0.7181,0.0450</t>
+  </si>
+  <si>
+    <t>0.9683,0.0023,0.0055,0.0095</t>
+  </si>
+  <si>
+    <t>0.0290,0.0203,0.0021,0.9792</t>
+  </si>
+  <si>
+    <t>0.0044,0.0020,0.0005,0.9975</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0009,0.9994</t>
+  </si>
+  <si>
+    <t>0.0040,0.0006,0.0005,0.9977</t>
+  </si>
+  <si>
+    <t>0.6709,0.0059,0.0210,0.3272</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
